--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 03,08,26 лгрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 03,08,26 лгрсч ост зпф.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D25B4D-9C03-429C-9F52-D66BEE847A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837B7A4A-F787-41FB-AA42-FA5AB6B80ADA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -68,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -155,6 +160,12 @@
   </si>
   <si>
     <t>нужно увеличить продажи</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>10,08,</t>
   </si>
 </sst>
 </file>
@@ -751,34 +762,34 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
@@ -820,28 +831,30 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -912,7 +925,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>355.54599999999999</v>
+        <v>360</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -939,7 +952,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="4">
         <f>SUM(Z6:Z500)</f>
-        <v>144.24600000000001</v>
+        <v>147</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -967,10 +980,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C6" s="1">
         <v>31</v>
@@ -991,7 +1004,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1033,10 +1046,10 @@
         <v>0</v>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z6" s="1">
-        <f>G6*Q6</f>
+        <f t="shared" ref="Z6:Z16" si="2">G6*Q6</f>
         <v>0</v>
       </c>
       <c r="AA6" s="1"/>
@@ -1065,10 +1078,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C7" s="1">
         <v>63</v>
@@ -1089,7 +1102,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1103,16 +1116,15 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:P16" si="2">E7/5</f>
+        <f t="shared" ref="P7:P16" si="3">E7/5</f>
         <v>5.4</v>
       </c>
       <c r="Q7" s="5">
-        <f t="shared" ref="Q7:Q16" si="3">15*P7-F7</f>
-        <v>17.545999999999999</v>
+        <v>20</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" ref="R7:R16" si="4">(F7+Q7)/P7</f>
-        <v>14.999999999999998</v>
+        <v>15.454444444444444</v>
       </c>
       <c r="S7" s="1">
         <f t="shared" ref="S7:S16" si="5">F7/P7</f>
@@ -1135,8 +1147,8 @@
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1">
-        <f>G7*Q7</f>
-        <v>17.545999999999999</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
@@ -1164,10 +1176,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1">
         <v>270</v>
@@ -1186,7 +1198,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1200,7 +1212,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
       <c r="Q8" s="5"/>
@@ -1228,10 +1240,10 @@
         <v>0.9</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Z8" s="1">
-        <f>G8*Q8</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA8" s="1"/>
@@ -1260,10 +1272,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
@@ -1282,7 +1294,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1296,7 +1308,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="Q9" s="5"/>
@@ -1325,7 +1337,7 @@
       </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1">
-        <f>G9*Q9</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA9" s="1"/>
@@ -1354,10 +1366,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -1378,7 +1390,7 @@
         <v>120</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1392,7 +1404,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="Q10" s="5"/>
@@ -1421,7 +1433,7 @@
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1">
-        <f>G10*Q10</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA10" s="1"/>
@@ -1450,10 +1462,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1">
         <v>132</v>
@@ -1474,7 +1486,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1488,16 +1500,15 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>24.2</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" si="3"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14.958677685950414</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="5"/>
@@ -1520,8 +1531,8 @@
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1">
-        <f>G11*Q11</f>
-        <v>24.3</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
@@ -1549,10 +1560,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1">
         <v>190</v>
@@ -1573,7 +1584,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1587,7 +1598,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.6</v>
       </c>
       <c r="Q12" s="5"/>
@@ -1615,10 +1626,10 @@
         <v>12.4</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z12" s="1">
-        <f>G12*Q12</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA12" s="1"/>
@@ -1647,10 +1658,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1">
         <v>157</v>
@@ -1671,7 +1682,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1685,16 +1696,15 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12.4</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>15.080645161290322</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="5"/>
@@ -1717,8 +1727,8 @@
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1">
-        <f>G13*Q13</f>
-        <v>5.7</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
@@ -1746,10 +1756,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1">
         <v>74</v>
@@ -1770,7 +1780,7 @@
         <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1784,16 +1794,15 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14.8</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" si="3"/>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>15.135135135135135</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="5"/>
@@ -1816,8 +1825,8 @@
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1">
-        <f>G14*Q14</f>
-        <v>34.299999999999997</v>
+        <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
@@ -1845,10 +1854,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1">
         <v>11</v>
@@ -1869,7 +1878,7 @@
         <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -1883,16 +1892,15 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.6</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="3"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>15.086206896551724</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" si="5"/>
@@ -1915,8 +1923,8 @@
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1">
-        <f>G15*Q15</f>
-        <v>26.7</v>
+        <f t="shared" si="2"/>
+        <v>27</v>
       </c>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
@@ -1944,10 +1952,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
@@ -1966,7 +1974,7 @@
         <v>180</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -1980,16 +1988,15 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14.8</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" si="3"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R16" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14.932432432432432</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="5"/>
@@ -2012,8 +2019,8 @@
       </c>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1">
-        <f>G16*Q16</f>
-        <v>35.699999999999996</v>
+        <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
